--- a/templates/team_project_capacity_workbook_template.xlsx
+++ b/templates/team_project_capacity_workbook_template.xlsx
@@ -12,10 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allocations" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacity" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIREF Members" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIREF Slots" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIREF Placeholders" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIREF Placeholder Allocations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIREF Requests" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +506,11 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>effective_end</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>next_hiref_id</t>
         </is>
       </c>
     </row>
@@ -569,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,6 +593,11 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>allocation</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hiref_id</t>
         </is>
       </c>
     </row>
@@ -646,32 +653,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>member_key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>next_hiref_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -683,7 +664,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>project_key</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -704,93 +685,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>notes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>placeholder_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>hiref_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>linked_member_key</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>resource_type</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>placeholder_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>project_key</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>allocation</t>
         </is>
       </c>
     </row>
